--- a/Data/Export/Common/Official_官职.xlsx
+++ b/Data/Export/Common/Official_官职.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B36C074-6D88-4727-8A7D-42A492374E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD638A07-A7CB-4C9A-915A-B80812256116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34245" yWindow="1710" windowWidth="21600" windowHeight="11355" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Officials" sheetId="36" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="435">
   <si>
     <t>备注:</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1374,6 +1374,10 @@
   </si>
   <si>
     <t>大司马都督中外，冠三军之首（统率+9，武力+10，智力+8，政治+6，魅力+7）</t>
+  </si>
+  <si>
+    <t>15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4669,8 +4673,8 @@
       <c r="E5" s="2">
         <v>5</v>
       </c>
-      <c r="F5" s="2">
-        <v>10</v>
+      <c r="F5" s="2" t="s">
+        <v>434</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>211</v>
@@ -4684,10 +4688,12 @@
         <v>212</v>
       </c>
       <c r="D6" s="2">
-        <v>5000</v>
+        <f>$D$5+(15-F6)*300</f>
+        <v>4800</v>
       </c>
       <c r="E6" s="2">
-        <v>20</v>
+        <f>$E$5+(15-F6)*3</f>
+        <v>8</v>
       </c>
       <c r="F6" s="2">
         <v>14</v>
@@ -4745,10 +4751,12 @@
         <v>214</v>
       </c>
       <c r="D7" s="2">
-        <v>5000</v>
+        <f t="shared" ref="D7:D70" si="0">$D$5+(15-F7)*300</f>
+        <v>4800</v>
       </c>
       <c r="E7" s="2">
-        <v>20</v>
+        <f t="shared" ref="E7:E70" si="1">$E$5+(15-F7)*3</f>
+        <v>8</v>
       </c>
       <c r="F7" s="2">
         <v>14</v>
@@ -4805,10 +4813,12 @@
         <v>216</v>
       </c>
       <c r="D8" s="2">
-        <v>5000</v>
+        <f t="shared" si="0"/>
+        <v>4800</v>
       </c>
       <c r="E8" s="2">
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="F8" s="2">
         <v>14</v>
@@ -4865,10 +4875,12 @@
         <v>218</v>
       </c>
       <c r="D9" s="2">
-        <v>5000</v>
+        <f t="shared" si="0"/>
+        <v>4800</v>
       </c>
       <c r="E9" s="2">
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="F9" s="2">
         <v>14</v>
@@ -4925,10 +4937,12 @@
         <v>220</v>
       </c>
       <c r="D10" s="2">
-        <v>5000</v>
+        <f t="shared" si="0"/>
+        <v>4800</v>
       </c>
       <c r="E10" s="2">
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="F10" s="2">
         <v>14</v>
@@ -4985,10 +4999,12 @@
         <v>222</v>
       </c>
       <c r="D11" s="2">
-        <v>5000</v>
+        <f t="shared" si="0"/>
+        <v>4800</v>
       </c>
       <c r="E11" s="2">
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="F11" s="2">
         <v>14</v>
@@ -5045,10 +5061,12 @@
         <v>224</v>
       </c>
       <c r="D12" s="2">
-        <v>5000</v>
+        <f t="shared" si="0"/>
+        <v>4800</v>
       </c>
       <c r="E12" s="2">
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="F12" s="2">
         <v>14</v>
@@ -5105,10 +5123,12 @@
         <v>226</v>
       </c>
       <c r="D13" s="2">
-        <v>5000</v>
+        <f t="shared" si="0"/>
+        <v>4800</v>
       </c>
       <c r="E13" s="2">
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="F13" s="2">
         <v>14</v>
@@ -5165,10 +5185,12 @@
         <v>228</v>
       </c>
       <c r="D14" s="2">
-        <v>5400</v>
+        <f t="shared" si="0"/>
+        <v>5100</v>
       </c>
       <c r="E14" s="2">
-        <v>28</v>
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
       <c r="F14" s="2">
         <v>13</v>
@@ -5225,10 +5247,12 @@
         <v>230</v>
       </c>
       <c r="D15" s="2">
-        <v>5400</v>
+        <f t="shared" si="0"/>
+        <v>5100</v>
       </c>
       <c r="E15" s="2">
-        <v>28</v>
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
       <c r="F15" s="2">
         <v>13</v>
@@ -5285,10 +5309,12 @@
         <v>232</v>
       </c>
       <c r="D16" s="2">
-        <v>5400</v>
+        <f t="shared" si="0"/>
+        <v>5100</v>
       </c>
       <c r="E16" s="2">
-        <v>28</v>
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
       <c r="F16" s="2">
         <v>13</v>
@@ -5345,10 +5371,12 @@
         <v>234</v>
       </c>
       <c r="D17" s="2">
-        <v>5400</v>
+        <f t="shared" si="0"/>
+        <v>5100</v>
       </c>
       <c r="E17" s="2">
-        <v>28</v>
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
       <c r="F17" s="2">
         <v>13</v>
@@ -5405,10 +5433,12 @@
         <v>236</v>
       </c>
       <c r="D18" s="2">
-        <v>5400</v>
+        <f t="shared" si="0"/>
+        <v>5100</v>
       </c>
       <c r="E18" s="2">
-        <v>28</v>
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
       <c r="F18" s="2">
         <v>13</v>
@@ -5465,10 +5495,12 @@
         <v>238</v>
       </c>
       <c r="D19" s="2">
-        <v>5400</v>
+        <f t="shared" si="0"/>
+        <v>5100</v>
       </c>
       <c r="E19" s="2">
-        <v>28</v>
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
       <c r="F19" s="2">
         <v>13</v>
@@ -5525,10 +5557,12 @@
         <v>240</v>
       </c>
       <c r="D20" s="2">
-        <v>5400</v>
+        <f t="shared" si="0"/>
+        <v>5100</v>
       </c>
       <c r="E20" s="2">
-        <v>28</v>
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
       <c r="F20" s="2">
         <v>13</v>
@@ -5585,10 +5619,12 @@
         <v>242</v>
       </c>
       <c r="D21" s="2">
-        <v>5400</v>
+        <f t="shared" si="0"/>
+        <v>5100</v>
       </c>
       <c r="E21" s="2">
-        <v>28</v>
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
       <c r="F21" s="2">
         <v>13</v>
@@ -5644,11 +5680,13 @@
       <c r="C22" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D22" s="4">
-        <v>5800</v>
+      <c r="D22" s="2">
+        <f t="shared" si="0"/>
+        <v>5400</v>
       </c>
       <c r="E22" s="2">
-        <v>36</v>
+        <f t="shared" si="1"/>
+        <v>14</v>
       </c>
       <c r="F22" s="4">
         <v>12</v>
@@ -5704,11 +5742,13 @@
       <c r="C23" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D23" s="4">
-        <v>5800</v>
+      <c r="D23" s="2">
+        <f t="shared" si="0"/>
+        <v>5400</v>
       </c>
       <c r="E23" s="2">
-        <v>36</v>
+        <f t="shared" si="1"/>
+        <v>14</v>
       </c>
       <c r="F23" s="4">
         <v>12</v>
@@ -5764,11 +5804,13 @@
       <c r="C24" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D24" s="4">
-        <v>5800</v>
+      <c r="D24" s="2">
+        <f t="shared" si="0"/>
+        <v>5400</v>
       </c>
       <c r="E24" s="2">
-        <v>36</v>
+        <f t="shared" si="1"/>
+        <v>14</v>
       </c>
       <c r="F24" s="4">
         <v>12</v>
@@ -5824,11 +5866,13 @@
       <c r="C25" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="D25" s="4">
-        <v>5800</v>
+      <c r="D25" s="2">
+        <f t="shared" si="0"/>
+        <v>5400</v>
       </c>
       <c r="E25" s="2">
-        <v>36</v>
+        <f t="shared" si="1"/>
+        <v>14</v>
       </c>
       <c r="F25" s="4">
         <v>12</v>
@@ -5884,11 +5928,13 @@
       <c r="C26" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="D26" s="4">
-        <v>5800</v>
+      <c r="D26" s="2">
+        <f t="shared" si="0"/>
+        <v>5400</v>
       </c>
       <c r="E26" s="2">
-        <v>36</v>
+        <f t="shared" si="1"/>
+        <v>14</v>
       </c>
       <c r="F26" s="4">
         <v>12</v>
@@ -5944,11 +5990,13 @@
       <c r="C27" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="D27" s="4">
-        <v>5800</v>
+      <c r="D27" s="2">
+        <f t="shared" si="0"/>
+        <v>5400</v>
       </c>
       <c r="E27" s="2">
-        <v>36</v>
+        <f t="shared" si="1"/>
+        <v>14</v>
       </c>
       <c r="F27" s="4">
         <v>12</v>
@@ -6004,11 +6052,13 @@
       <c r="C28" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="D28" s="4">
-        <v>5800</v>
+      <c r="D28" s="2">
+        <f t="shared" si="0"/>
+        <v>5400</v>
       </c>
       <c r="E28" s="2">
-        <v>36</v>
+        <f t="shared" si="1"/>
+        <v>14</v>
       </c>
       <c r="F28" s="4">
         <v>12</v>
@@ -6064,11 +6114,13 @@
       <c r="C29" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D29" s="4">
-        <v>5800</v>
+      <c r="D29" s="2">
+        <f t="shared" si="0"/>
+        <v>5400</v>
       </c>
       <c r="E29" s="2">
-        <v>36</v>
+        <f t="shared" si="1"/>
+        <v>14</v>
       </c>
       <c r="F29" s="4">
         <v>12</v>
@@ -6124,11 +6176,13 @@
       <c r="C30" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="D30" s="4">
-        <v>6300</v>
+      <c r="D30" s="2">
+        <f t="shared" si="0"/>
+        <v>5700</v>
       </c>
       <c r="E30" s="2">
-        <v>46</v>
+        <f t="shared" si="1"/>
+        <v>17</v>
       </c>
       <c r="F30" s="4">
         <v>11</v>
@@ -6184,11 +6238,13 @@
       <c r="C31" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="D31" s="4">
-        <v>6300</v>
+      <c r="D31" s="2">
+        <f t="shared" si="0"/>
+        <v>5700</v>
       </c>
       <c r="E31" s="2">
-        <v>46</v>
+        <f t="shared" si="1"/>
+        <v>17</v>
       </c>
       <c r="F31" s="4">
         <v>11</v>
@@ -6244,11 +6300,13 @@
       <c r="C32" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="D32" s="4">
-        <v>6300</v>
+      <c r="D32" s="2">
+        <f t="shared" si="0"/>
+        <v>5700</v>
       </c>
       <c r="E32" s="2">
-        <v>46</v>
+        <f t="shared" si="1"/>
+        <v>17</v>
       </c>
       <c r="F32" s="4">
         <v>11</v>
@@ -6304,11 +6362,13 @@
       <c r="C33" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="D33" s="4">
-        <v>6300</v>
+      <c r="D33" s="2">
+        <f t="shared" si="0"/>
+        <v>5700</v>
       </c>
       <c r="E33" s="2">
-        <v>46</v>
+        <f t="shared" si="1"/>
+        <v>17</v>
       </c>
       <c r="F33" s="4">
         <v>11</v>
@@ -6364,11 +6424,13 @@
       <c r="C34" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="D34" s="4">
-        <v>6300</v>
+      <c r="D34" s="2">
+        <f t="shared" si="0"/>
+        <v>5700</v>
       </c>
       <c r="E34" s="2">
-        <v>46</v>
+        <f t="shared" si="1"/>
+        <v>17</v>
       </c>
       <c r="F34" s="4">
         <v>11</v>
@@ -6424,11 +6486,13 @@
       <c r="C35" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D35" s="4">
-        <v>6300</v>
+      <c r="D35" s="2">
+        <f t="shared" si="0"/>
+        <v>5700</v>
       </c>
       <c r="E35" s="2">
-        <v>46</v>
+        <f t="shared" si="1"/>
+        <v>17</v>
       </c>
       <c r="F35" s="4">
         <v>11</v>
@@ -6484,11 +6548,13 @@
       <c r="C36" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="D36" s="4">
-        <v>6300</v>
+      <c r="D36" s="2">
+        <f t="shared" si="0"/>
+        <v>5700</v>
       </c>
       <c r="E36" s="2">
-        <v>46</v>
+        <f t="shared" si="1"/>
+        <v>17</v>
       </c>
       <c r="F36" s="4">
         <v>11</v>
@@ -6544,11 +6610,13 @@
       <c r="C37" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="D37" s="4">
-        <v>6300</v>
+      <c r="D37" s="2">
+        <f t="shared" si="0"/>
+        <v>5700</v>
       </c>
       <c r="E37" s="2">
-        <v>46</v>
+        <f t="shared" si="1"/>
+        <v>17</v>
       </c>
       <c r="F37" s="4">
         <v>11</v>
@@ -6604,11 +6672,13 @@
       <c r="C38" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="D38" s="4">
-        <v>6800</v>
+      <c r="D38" s="2">
+        <f t="shared" si="0"/>
+        <v>6000</v>
       </c>
       <c r="E38" s="2">
-        <v>58</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="F38" s="4">
         <v>10</v>
@@ -6664,11 +6734,13 @@
       <c r="C39" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D39" s="4">
-        <v>6800</v>
+      <c r="D39" s="2">
+        <f t="shared" si="0"/>
+        <v>6000</v>
       </c>
       <c r="E39" s="2">
-        <v>58</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="F39" s="4">
         <v>10</v>
@@ -6724,11 +6796,13 @@
       <c r="C40" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D40" s="4">
-        <v>6800</v>
+      <c r="D40" s="2">
+        <f t="shared" si="0"/>
+        <v>6000</v>
       </c>
       <c r="E40" s="2">
-        <v>58</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="F40" s="4">
         <v>10</v>
@@ -6784,11 +6858,13 @@
       <c r="C41" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D41" s="4">
-        <v>6800</v>
+      <c r="D41" s="2">
+        <f t="shared" si="0"/>
+        <v>6000</v>
       </c>
       <c r="E41" s="2">
-        <v>58</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="F41" s="4">
         <v>10</v>
@@ -6844,11 +6920,13 @@
       <c r="C42" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D42" s="4">
-        <v>6800</v>
+      <c r="D42" s="2">
+        <f t="shared" si="0"/>
+        <v>6000</v>
       </c>
       <c r="E42" s="2">
-        <v>58</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="F42" s="4">
         <v>10</v>
@@ -6904,11 +6982,13 @@
       <c r="C43" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="D43" s="4">
-        <v>6800</v>
+      <c r="D43" s="2">
+        <f t="shared" si="0"/>
+        <v>6000</v>
       </c>
       <c r="E43" s="2">
-        <v>58</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="F43" s="4">
         <v>10</v>
@@ -6964,11 +7044,13 @@
       <c r="C44" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D44" s="4">
-        <v>6800</v>
-      </c>
-      <c r="E44" s="6">
-        <v>58</v>
+      <c r="D44" s="2">
+        <f t="shared" si="0"/>
+        <v>6000</v>
+      </c>
+      <c r="E44" s="2">
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="F44" s="4">
         <v>10</v>
@@ -7024,11 +7106,13 @@
       <c r="C45" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D45" s="4">
-        <v>6800</v>
-      </c>
-      <c r="E45" s="6">
-        <v>58</v>
+      <c r="D45" s="2">
+        <f t="shared" si="0"/>
+        <v>6000</v>
+      </c>
+      <c r="E45" s="2">
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="F45" s="4">
         <v>10</v>
@@ -7084,11 +7168,13 @@
       <c r="C46" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="D46" s="4">
-        <v>7400</v>
-      </c>
-      <c r="E46" s="6">
-        <v>72</v>
+      <c r="D46" s="2">
+        <f t="shared" si="0"/>
+        <v>6300</v>
+      </c>
+      <c r="E46" s="2">
+        <f t="shared" si="1"/>
+        <v>23</v>
       </c>
       <c r="F46" s="4">
         <v>9</v>
@@ -7144,11 +7230,13 @@
       <c r="C47" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="D47" s="4">
-        <v>7400</v>
-      </c>
-      <c r="E47" s="6">
-        <v>72</v>
+      <c r="D47" s="2">
+        <f t="shared" si="0"/>
+        <v>6300</v>
+      </c>
+      <c r="E47" s="2">
+        <f t="shared" si="1"/>
+        <v>23</v>
       </c>
       <c r="F47" s="4">
         <v>9</v>
@@ -7201,11 +7289,13 @@
       <c r="C48" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="D48" s="4">
-        <v>7400</v>
-      </c>
-      <c r="E48" s="6">
-        <v>72</v>
+      <c r="D48" s="2">
+        <f t="shared" si="0"/>
+        <v>6300</v>
+      </c>
+      <c r="E48" s="2">
+        <f t="shared" si="1"/>
+        <v>23</v>
       </c>
       <c r="F48" s="4">
         <v>9</v>
@@ -7257,11 +7347,13 @@
       <c r="C49" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="D49" s="4">
-        <v>7400</v>
-      </c>
-      <c r="E49" s="6">
-        <v>72</v>
+      <c r="D49" s="2">
+        <f t="shared" si="0"/>
+        <v>6300</v>
+      </c>
+      <c r="E49" s="2">
+        <f t="shared" si="1"/>
+        <v>23</v>
       </c>
       <c r="F49" s="4">
         <v>9</v>
@@ -7313,11 +7405,13 @@
       <c r="C50" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="D50" s="4">
-        <v>7400</v>
-      </c>
-      <c r="E50" s="6">
-        <v>72</v>
+      <c r="D50" s="2">
+        <f t="shared" si="0"/>
+        <v>6300</v>
+      </c>
+      <c r="E50" s="2">
+        <f t="shared" si="1"/>
+        <v>23</v>
       </c>
       <c r="F50" s="4">
         <v>9</v>
@@ -7369,11 +7463,13 @@
       <c r="C51" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="D51" s="4">
-        <v>7400</v>
-      </c>
-      <c r="E51" s="6">
-        <v>72</v>
+      <c r="D51" s="2">
+        <f t="shared" si="0"/>
+        <v>6300</v>
+      </c>
+      <c r="E51" s="2">
+        <f t="shared" si="1"/>
+        <v>23</v>
       </c>
       <c r="F51" s="4">
         <v>9</v>
@@ -7425,11 +7521,13 @@
       <c r="C52" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="D52" s="4">
-        <v>7400</v>
-      </c>
-      <c r="E52" s="6">
-        <v>72</v>
+      <c r="D52" s="2">
+        <f t="shared" si="0"/>
+        <v>6300</v>
+      </c>
+      <c r="E52" s="2">
+        <f t="shared" si="1"/>
+        <v>23</v>
       </c>
       <c r="F52" s="4">
         <v>9</v>
@@ -7481,11 +7579,13 @@
       <c r="C53" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="D53" s="4">
-        <v>7400</v>
+      <c r="D53" s="2">
+        <f t="shared" si="0"/>
+        <v>6300</v>
       </c>
       <c r="E53" s="2">
-        <v>72</v>
+        <f t="shared" si="1"/>
+        <v>23</v>
       </c>
       <c r="F53" s="4">
         <v>9</v>
@@ -7537,11 +7637,13 @@
       <c r="C54" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="D54" s="4">
-        <v>8000</v>
-      </c>
-      <c r="E54" s="6">
-        <v>88</v>
+      <c r="D54" s="2">
+        <f t="shared" si="0"/>
+        <v>6600</v>
+      </c>
+      <c r="E54" s="2">
+        <f t="shared" si="1"/>
+        <v>26</v>
       </c>
       <c r="F54" s="4">
         <v>8</v>
@@ -7593,11 +7695,13 @@
       <c r="C55" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="D55" s="4">
-        <v>8000</v>
-      </c>
-      <c r="E55" s="6">
-        <v>88</v>
+      <c r="D55" s="2">
+        <f t="shared" si="0"/>
+        <v>6600</v>
+      </c>
+      <c r="E55" s="2">
+        <f t="shared" si="1"/>
+        <v>26</v>
       </c>
       <c r="F55" s="4">
         <v>8</v>
@@ -7649,11 +7753,13 @@
       <c r="C56" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="D56" s="4">
-        <v>8000</v>
-      </c>
-      <c r="E56" s="6">
-        <v>88</v>
+      <c r="D56" s="2">
+        <f t="shared" si="0"/>
+        <v>6600</v>
+      </c>
+      <c r="E56" s="2">
+        <f t="shared" si="1"/>
+        <v>26</v>
       </c>
       <c r="F56" s="4">
         <v>8</v>
@@ -7705,11 +7811,13 @@
       <c r="C57" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="D57" s="4">
-        <v>8000</v>
-      </c>
-      <c r="E57" s="6">
-        <v>88</v>
+      <c r="D57" s="2">
+        <f t="shared" si="0"/>
+        <v>6600</v>
+      </c>
+      <c r="E57" s="2">
+        <f t="shared" si="1"/>
+        <v>26</v>
       </c>
       <c r="F57" s="4">
         <v>8</v>
@@ -7761,11 +7869,13 @@
       <c r="C58" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="D58" s="4">
-        <v>8000</v>
-      </c>
-      <c r="E58" s="6">
-        <v>88</v>
+      <c r="D58" s="2">
+        <f t="shared" si="0"/>
+        <v>6600</v>
+      </c>
+      <c r="E58" s="2">
+        <f t="shared" si="1"/>
+        <v>26</v>
       </c>
       <c r="F58" s="4">
         <v>8</v>
@@ -7817,11 +7927,13 @@
       <c r="C59" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="D59" s="4">
-        <v>8000</v>
-      </c>
-      <c r="E59" s="6">
-        <v>88</v>
+      <c r="D59" s="2">
+        <f t="shared" si="0"/>
+        <v>6600</v>
+      </c>
+      <c r="E59" s="2">
+        <f t="shared" si="1"/>
+        <v>26</v>
       </c>
       <c r="F59" s="4">
         <v>8</v>
@@ -7873,11 +7985,13 @@
       <c r="C60" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="D60" s="4">
-        <v>8000</v>
-      </c>
-      <c r="E60" s="6">
-        <v>88</v>
+      <c r="D60" s="2">
+        <f t="shared" si="0"/>
+        <v>6600</v>
+      </c>
+      <c r="E60" s="2">
+        <f t="shared" si="1"/>
+        <v>26</v>
       </c>
       <c r="F60" s="4">
         <v>8</v>
@@ -7929,11 +8043,13 @@
       <c r="C61" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="D61" s="4">
-        <v>8000</v>
-      </c>
-      <c r="E61" s="6">
-        <v>88</v>
+      <c r="D61" s="2">
+        <f t="shared" si="0"/>
+        <v>6600</v>
+      </c>
+      <c r="E61" s="2">
+        <f t="shared" si="1"/>
+        <v>26</v>
       </c>
       <c r="F61" s="4">
         <v>8</v>
@@ -7985,11 +8101,13 @@
       <c r="C62" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="D62" s="4">
-        <v>8000</v>
-      </c>
-      <c r="E62" s="6">
-        <v>88</v>
+      <c r="D62" s="2">
+        <f t="shared" si="0"/>
+        <v>6600</v>
+      </c>
+      <c r="E62" s="2">
+        <f t="shared" si="1"/>
+        <v>26</v>
       </c>
       <c r="F62" s="4">
         <v>8</v>
@@ -8041,11 +8159,13 @@
       <c r="C63" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="D63" s="4">
-        <v>8700</v>
-      </c>
-      <c r="E63" s="6">
-        <v>106</v>
+      <c r="D63" s="2">
+        <f t="shared" si="0"/>
+        <v>6900</v>
+      </c>
+      <c r="E63" s="2">
+        <f t="shared" si="1"/>
+        <v>29</v>
       </c>
       <c r="F63" s="4">
         <v>7</v>
@@ -8097,11 +8217,13 @@
       <c r="C64" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="D64" s="4">
-        <v>8700</v>
-      </c>
-      <c r="E64" s="6">
-        <v>106</v>
+      <c r="D64" s="2">
+        <f t="shared" si="0"/>
+        <v>6900</v>
+      </c>
+      <c r="E64" s="2">
+        <f t="shared" si="1"/>
+        <v>29</v>
       </c>
       <c r="F64" s="4">
         <v>7</v>
@@ -8153,11 +8275,13 @@
       <c r="C65" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="D65" s="4">
-        <v>8700</v>
-      </c>
-      <c r="E65" s="6">
-        <v>106</v>
+      <c r="D65" s="2">
+        <f t="shared" si="0"/>
+        <v>6900</v>
+      </c>
+      <c r="E65" s="2">
+        <f t="shared" si="1"/>
+        <v>29</v>
       </c>
       <c r="F65" s="4">
         <v>7</v>
@@ -8209,11 +8333,13 @@
       <c r="C66" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="D66" s="4">
-        <v>8700</v>
-      </c>
-      <c r="E66" s="6">
-        <v>106</v>
+      <c r="D66" s="2">
+        <f t="shared" si="0"/>
+        <v>6900</v>
+      </c>
+      <c r="E66" s="2">
+        <f t="shared" si="1"/>
+        <v>29</v>
       </c>
       <c r="F66" s="4">
         <v>7</v>
@@ -8265,11 +8391,13 @@
       <c r="C67" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="D67" s="4">
-        <v>8700</v>
-      </c>
-      <c r="E67" s="6">
-        <v>106</v>
+      <c r="D67" s="2">
+        <f t="shared" si="0"/>
+        <v>6900</v>
+      </c>
+      <c r="E67" s="2">
+        <f t="shared" si="1"/>
+        <v>29</v>
       </c>
       <c r="F67" s="4">
         <v>7</v>
@@ -8321,11 +8449,13 @@
       <c r="C68" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D68" s="4">
-        <v>8700</v>
-      </c>
-      <c r="E68" s="6">
-        <v>106</v>
+      <c r="D68" s="2">
+        <f t="shared" si="0"/>
+        <v>6900</v>
+      </c>
+      <c r="E68" s="2">
+        <f t="shared" si="1"/>
+        <v>29</v>
       </c>
       <c r="F68" s="4">
         <v>7</v>
@@ -8377,11 +8507,13 @@
       <c r="C69" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D69" s="4">
-        <v>8700</v>
-      </c>
-      <c r="E69" s="6">
-        <v>106</v>
+      <c r="D69" s="2">
+        <f t="shared" si="0"/>
+        <v>6900</v>
+      </c>
+      <c r="E69" s="2">
+        <f t="shared" si="1"/>
+        <v>29</v>
       </c>
       <c r="F69" s="4">
         <v>7</v>
@@ -8433,11 +8565,13 @@
       <c r="C70" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D70" s="4">
-        <v>8700</v>
-      </c>
-      <c r="E70" s="6">
-        <v>106</v>
+      <c r="D70" s="2">
+        <f t="shared" si="0"/>
+        <v>6900</v>
+      </c>
+      <c r="E70" s="2">
+        <f t="shared" si="1"/>
+        <v>29</v>
       </c>
       <c r="F70" s="4">
         <v>7</v>
@@ -8489,11 +8623,13 @@
       <c r="C71" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D71" s="4">
-        <v>8700</v>
-      </c>
-      <c r="E71" s="6">
-        <v>106</v>
+      <c r="D71" s="2">
+        <f t="shared" ref="D71:D134" si="2">$D$5+(15-F71)*300</f>
+        <v>6900</v>
+      </c>
+      <c r="E71" s="2">
+        <f t="shared" ref="E71:E134" si="3">$E$5+(15-F71)*3</f>
+        <v>29</v>
       </c>
       <c r="F71" s="4">
         <v>7</v>
@@ -8545,11 +8681,13 @@
       <c r="C72" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="D72" s="4">
-        <v>9500</v>
-      </c>
-      <c r="E72" s="6">
-        <v>126</v>
+      <c r="D72" s="2">
+        <f t="shared" si="2"/>
+        <v>7200</v>
+      </c>
+      <c r="E72" s="2">
+        <f t="shared" si="3"/>
+        <v>32</v>
       </c>
       <c r="F72" s="4">
         <v>6</v>
@@ -8601,11 +8739,13 @@
       <c r="C73" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D73" s="4">
-        <v>9500</v>
-      </c>
-      <c r="E73" s="6">
-        <v>126</v>
+      <c r="D73" s="2">
+        <f t="shared" si="2"/>
+        <v>7200</v>
+      </c>
+      <c r="E73" s="2">
+        <f t="shared" si="3"/>
+        <v>32</v>
       </c>
       <c r="F73" s="4">
         <v>6</v>
@@ -8657,11 +8797,13 @@
       <c r="C74" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="D74" s="4">
-        <v>9500</v>
-      </c>
-      <c r="E74" s="6">
-        <v>126</v>
+      <c r="D74" s="2">
+        <f t="shared" si="2"/>
+        <v>7200</v>
+      </c>
+      <c r="E74" s="2">
+        <f t="shared" si="3"/>
+        <v>32</v>
       </c>
       <c r="F74" s="4">
         <v>6</v>
@@ -8713,11 +8855,13 @@
       <c r="C75" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="D75" s="4">
-        <v>9500</v>
-      </c>
-      <c r="E75" s="6">
-        <v>126</v>
+      <c r="D75" s="2">
+        <f t="shared" si="2"/>
+        <v>7200</v>
+      </c>
+      <c r="E75" s="2">
+        <f t="shared" si="3"/>
+        <v>32</v>
       </c>
       <c r="F75" s="4">
         <v>6</v>
@@ -8769,11 +8913,13 @@
       <c r="C76" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D76" s="4">
-        <v>9500</v>
-      </c>
-      <c r="E76" s="6">
-        <v>126</v>
+      <c r="D76" s="2">
+        <f t="shared" si="2"/>
+        <v>7200</v>
+      </c>
+      <c r="E76" s="2">
+        <f t="shared" si="3"/>
+        <v>32</v>
       </c>
       <c r="F76" s="4">
         <v>6</v>
@@ -8825,11 +8971,13 @@
       <c r="C77" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D77" s="4">
-        <v>9500</v>
-      </c>
-      <c r="E77" s="6">
-        <v>126</v>
+      <c r="D77" s="2">
+        <f t="shared" si="2"/>
+        <v>7200</v>
+      </c>
+      <c r="E77" s="2">
+        <f t="shared" si="3"/>
+        <v>32</v>
       </c>
       <c r="F77" s="4">
         <v>6</v>
@@ -8881,11 +9029,13 @@
       <c r="C78" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D78" s="4">
-        <v>9500</v>
-      </c>
-      <c r="E78" s="6">
-        <v>126</v>
+      <c r="D78" s="2">
+        <f t="shared" si="2"/>
+        <v>7200</v>
+      </c>
+      <c r="E78" s="2">
+        <f t="shared" si="3"/>
+        <v>32</v>
       </c>
       <c r="F78" s="4">
         <v>6</v>
@@ -8937,11 +9087,13 @@
       <c r="C79" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D79" s="4">
-        <v>9500</v>
-      </c>
-      <c r="E79" s="6">
-        <v>126</v>
+      <c r="D79" s="2">
+        <f t="shared" si="2"/>
+        <v>7200</v>
+      </c>
+      <c r="E79" s="2">
+        <f t="shared" si="3"/>
+        <v>32</v>
       </c>
       <c r="F79" s="4">
         <v>6</v>
@@ -8993,11 +9145,13 @@
       <c r="C80" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D80" s="4">
-        <v>9500</v>
-      </c>
-      <c r="E80" s="6">
-        <v>126</v>
+      <c r="D80" s="2">
+        <f t="shared" si="2"/>
+        <v>7200</v>
+      </c>
+      <c r="E80" s="2">
+        <f t="shared" si="3"/>
+        <v>32</v>
       </c>
       <c r="F80" s="4">
         <v>6</v>
@@ -9049,11 +9203,13 @@
       <c r="C81" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D81" s="4">
-        <v>10400</v>
-      </c>
-      <c r="E81" s="6">
-        <v>150</v>
+      <c r="D81" s="2">
+        <f t="shared" si="2"/>
+        <v>7500</v>
+      </c>
+      <c r="E81" s="2">
+        <f t="shared" si="3"/>
+        <v>35</v>
       </c>
       <c r="F81" s="4">
         <v>5</v>
@@ -9105,11 +9261,13 @@
       <c r="C82" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D82" s="4">
-        <v>10400</v>
-      </c>
-      <c r="E82" s="6">
-        <v>150</v>
+      <c r="D82" s="2">
+        <f t="shared" si="2"/>
+        <v>7500</v>
+      </c>
+      <c r="E82" s="2">
+        <f t="shared" si="3"/>
+        <v>35</v>
       </c>
       <c r="F82" s="4">
         <v>5</v>
@@ -9161,11 +9319,13 @@
       <c r="C83" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D83" s="4">
-        <v>10400</v>
-      </c>
-      <c r="E83" s="6">
-        <v>150</v>
+      <c r="D83" s="2">
+        <f t="shared" si="2"/>
+        <v>7500</v>
+      </c>
+      <c r="E83" s="2">
+        <f t="shared" si="3"/>
+        <v>35</v>
       </c>
       <c r="F83" s="4">
         <v>5</v>
@@ -9217,11 +9377,13 @@
       <c r="C84" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D84" s="4">
-        <v>10400</v>
-      </c>
-      <c r="E84" s="6">
-        <v>150</v>
+      <c r="D84" s="2">
+        <f t="shared" si="2"/>
+        <v>7500</v>
+      </c>
+      <c r="E84" s="2">
+        <f t="shared" si="3"/>
+        <v>35</v>
       </c>
       <c r="F84" s="4">
         <v>5</v>
@@ -9273,11 +9435,13 @@
       <c r="C85" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D85" s="4">
-        <v>10400</v>
-      </c>
-      <c r="E85" s="6">
-        <v>150</v>
+      <c r="D85" s="2">
+        <f t="shared" si="2"/>
+        <v>7500</v>
+      </c>
+      <c r="E85" s="2">
+        <f t="shared" si="3"/>
+        <v>35</v>
       </c>
       <c r="F85" s="4">
         <v>5</v>
@@ -9330,10 +9494,12 @@
         <v>36</v>
       </c>
       <c r="D86" s="2">
-        <v>10400</v>
+        <f t="shared" si="2"/>
+        <v>7500</v>
       </c>
       <c r="E86" s="2">
-        <v>150</v>
+        <f t="shared" si="3"/>
+        <v>35</v>
       </c>
       <c r="F86" s="2">
         <v>5</v>
@@ -9386,10 +9552,12 @@
         <v>23</v>
       </c>
       <c r="D87" s="2">
-        <v>10400</v>
+        <f t="shared" si="2"/>
+        <v>7500</v>
       </c>
       <c r="E87" s="2">
-        <v>150</v>
+        <f t="shared" si="3"/>
+        <v>35</v>
       </c>
       <c r="F87" s="2">
         <v>5</v>
@@ -9442,10 +9610,12 @@
         <v>21</v>
       </c>
       <c r="D88" s="2">
-        <v>10400</v>
+        <f t="shared" si="2"/>
+        <v>7500</v>
       </c>
       <c r="E88" s="2">
-        <v>150</v>
+        <f t="shared" si="3"/>
+        <v>35</v>
       </c>
       <c r="F88" s="2">
         <v>5</v>
@@ -9498,10 +9668,12 @@
         <v>22</v>
       </c>
       <c r="D89" s="2">
-        <v>10400</v>
+        <f t="shared" si="2"/>
+        <v>7500</v>
       </c>
       <c r="E89" s="2">
-        <v>150</v>
+        <f t="shared" si="3"/>
+        <v>35</v>
       </c>
       <c r="F89" s="2">
         <v>5</v>
@@ -9554,10 +9726,12 @@
         <v>24</v>
       </c>
       <c r="D90" s="2">
-        <v>10400</v>
+        <f t="shared" si="2"/>
+        <v>7500</v>
       </c>
       <c r="E90" s="2">
-        <v>150</v>
+        <f t="shared" si="3"/>
+        <v>35</v>
       </c>
       <c r="F90" s="2">
         <v>5</v>
@@ -9610,10 +9784,12 @@
         <v>27</v>
       </c>
       <c r="D91" s="2">
-        <v>11300</v>
+        <f t="shared" si="2"/>
+        <v>7800</v>
       </c>
       <c r="E91" s="2">
-        <v>176</v>
+        <f t="shared" si="3"/>
+        <v>38</v>
       </c>
       <c r="F91" s="2">
         <v>4</v>
@@ -9666,10 +9842,12 @@
         <v>20</v>
       </c>
       <c r="D92" s="2">
-        <v>11300</v>
+        <f t="shared" si="2"/>
+        <v>7800</v>
       </c>
       <c r="E92" s="2">
-        <v>176</v>
+        <f t="shared" si="3"/>
+        <v>38</v>
       </c>
       <c r="F92" s="2">
         <v>4</v>
@@ -9722,10 +9900,12 @@
         <v>19</v>
       </c>
       <c r="D93" s="2">
-        <v>11300</v>
+        <f t="shared" si="2"/>
+        <v>7800</v>
       </c>
       <c r="E93" s="2">
-        <v>176</v>
+        <f t="shared" si="3"/>
+        <v>38</v>
       </c>
       <c r="F93" s="2">
         <v>4</v>
@@ -9778,10 +9958,12 @@
         <v>363</v>
       </c>
       <c r="D94" s="2">
-        <v>11300</v>
+        <f t="shared" si="2"/>
+        <v>7800</v>
       </c>
       <c r="E94" s="2">
-        <v>176</v>
+        <f t="shared" si="3"/>
+        <v>38</v>
       </c>
       <c r="F94" s="2">
         <v>4</v>
@@ -9834,10 +10016,12 @@
         <v>35</v>
       </c>
       <c r="D95" s="2">
-        <v>11300</v>
+        <f t="shared" si="2"/>
+        <v>7800</v>
       </c>
       <c r="E95" s="2">
-        <v>176</v>
+        <f t="shared" si="3"/>
+        <v>38</v>
       </c>
       <c r="F95" s="2">
         <v>4</v>
@@ -9890,10 +10074,12 @@
         <v>366</v>
       </c>
       <c r="D96" s="2">
-        <v>11300</v>
+        <f t="shared" si="2"/>
+        <v>7800</v>
       </c>
       <c r="E96" s="2">
-        <v>176</v>
+        <f t="shared" si="3"/>
+        <v>38</v>
       </c>
       <c r="F96" s="2">
         <v>4</v>
@@ -9946,10 +10132,12 @@
         <v>47</v>
       </c>
       <c r="D97" s="2">
-        <v>11300</v>
+        <f t="shared" si="2"/>
+        <v>7800</v>
       </c>
       <c r="E97" s="2">
-        <v>176</v>
+        <f t="shared" si="3"/>
+        <v>38</v>
       </c>
       <c r="F97" s="2">
         <v>4</v>
@@ -10002,10 +10190,12 @@
         <v>48</v>
       </c>
       <c r="D98" s="2">
-        <v>11300</v>
+        <f t="shared" si="2"/>
+        <v>7800</v>
       </c>
       <c r="E98" s="2">
-        <v>176</v>
+        <f t="shared" si="3"/>
+        <v>38</v>
       </c>
       <c r="F98" s="2">
         <v>4</v>
@@ -10058,10 +10248,12 @@
         <v>45</v>
       </c>
       <c r="D99" s="2">
-        <v>11300</v>
+        <f t="shared" si="2"/>
+        <v>7800</v>
       </c>
       <c r="E99" s="2">
-        <v>176</v>
+        <f t="shared" si="3"/>
+        <v>38</v>
       </c>
       <c r="F99" s="2">
         <v>4</v>
@@ -10114,10 +10306,12 @@
         <v>46</v>
       </c>
       <c r="D100" s="2">
-        <v>11300</v>
+        <f t="shared" si="2"/>
+        <v>7800</v>
       </c>
       <c r="E100" s="2">
-        <v>176</v>
+        <f t="shared" si="3"/>
+        <v>38</v>
       </c>
       <c r="F100" s="2">
         <v>4</v>
@@ -10170,10 +10364,12 @@
         <v>11</v>
       </c>
       <c r="D101" s="2">
-        <v>12200</v>
+        <f t="shared" si="2"/>
+        <v>8100</v>
       </c>
       <c r="E101" s="2">
-        <v>205</v>
+        <f t="shared" si="3"/>
+        <v>41</v>
       </c>
       <c r="F101" s="2">
         <v>3</v>
@@ -10226,10 +10422,12 @@
         <v>12</v>
       </c>
       <c r="D102" s="2">
-        <v>12200</v>
+        <f t="shared" si="2"/>
+        <v>8100</v>
       </c>
       <c r="E102" s="2">
-        <v>205</v>
+        <f t="shared" si="3"/>
+        <v>41</v>
       </c>
       <c r="F102" s="2">
         <v>3</v>
@@ -10282,10 +10480,12 @@
         <v>10</v>
       </c>
       <c r="D103" s="2">
-        <v>12200</v>
+        <f t="shared" si="2"/>
+        <v>8100</v>
       </c>
       <c r="E103" s="2">
-        <v>205</v>
+        <f t="shared" si="3"/>
+        <v>41</v>
       </c>
       <c r="F103" s="2">
         <v>3</v>
@@ -10338,10 +10538,12 @@
         <v>375</v>
       </c>
       <c r="D104" s="2">
-        <v>12200</v>
+        <f t="shared" si="2"/>
+        <v>8100</v>
       </c>
       <c r="E104" s="2">
-        <v>205</v>
+        <f t="shared" si="3"/>
+        <v>41</v>
       </c>
       <c r="F104" s="2">
         <v>3</v>
@@ -10394,10 +10596,12 @@
         <v>377</v>
       </c>
       <c r="D105" s="2">
-        <v>12200</v>
+        <f t="shared" si="2"/>
+        <v>8100</v>
       </c>
       <c r="E105" s="2">
-        <v>205</v>
+        <f t="shared" si="3"/>
+        <v>41</v>
       </c>
       <c r="F105" s="2">
         <v>3</v>
@@ -10450,10 +10654,12 @@
         <v>16</v>
       </c>
       <c r="D106" s="2">
-        <v>12200</v>
+        <f t="shared" si="2"/>
+        <v>8100</v>
       </c>
       <c r="E106" s="2">
-        <v>205</v>
+        <f t="shared" si="3"/>
+        <v>41</v>
       </c>
       <c r="F106" s="2">
         <v>3</v>
@@ -10506,10 +10712,12 @@
         <v>15</v>
       </c>
       <c r="D107" s="2">
-        <v>12200</v>
+        <f t="shared" si="2"/>
+        <v>8100</v>
       </c>
       <c r="E107" s="2">
-        <v>205</v>
+        <f t="shared" si="3"/>
+        <v>41</v>
       </c>
       <c r="F107" s="2">
         <v>3</v>
@@ -10562,10 +10770,12 @@
         <v>14</v>
       </c>
       <c r="D108" s="2">
-        <v>12200</v>
+        <f t="shared" si="2"/>
+        <v>8100</v>
       </c>
       <c r="E108" s="2">
-        <v>205</v>
+        <f t="shared" si="3"/>
+        <v>41</v>
       </c>
       <c r="F108" s="2">
         <v>3</v>
@@ -10618,10 +10828,12 @@
         <v>382</v>
       </c>
       <c r="D109" s="2">
-        <v>12200</v>
+        <f t="shared" si="2"/>
+        <v>8100</v>
       </c>
       <c r="E109" s="2">
-        <v>205</v>
+        <f t="shared" si="3"/>
+        <v>41</v>
       </c>
       <c r="F109" s="2">
         <v>3</v>
@@ -10674,10 +10886,12 @@
         <v>384</v>
       </c>
       <c r="D110" s="2">
-        <v>13100</v>
+        <f t="shared" si="2"/>
+        <v>8400</v>
       </c>
       <c r="E110" s="2">
-        <v>238</v>
+        <f t="shared" si="3"/>
+        <v>44</v>
       </c>
       <c r="F110" s="2">
         <v>2</v>
@@ -10730,10 +10944,12 @@
         <v>386</v>
       </c>
       <c r="D111" s="2">
-        <v>13100</v>
+        <f t="shared" si="2"/>
+        <v>8400</v>
       </c>
       <c r="E111" s="2">
-        <v>238</v>
+        <f t="shared" si="3"/>
+        <v>44</v>
       </c>
       <c r="F111" s="2">
         <v>2</v>
@@ -10786,10 +11002,12 @@
         <v>388</v>
       </c>
       <c r="D112" s="2">
-        <v>13100</v>
+        <f t="shared" si="2"/>
+        <v>8400</v>
       </c>
       <c r="E112" s="2">
-        <v>238</v>
+        <f t="shared" si="3"/>
+        <v>44</v>
       </c>
       <c r="F112" s="2">
         <v>2</v>
@@ -10842,10 +11060,12 @@
         <v>390</v>
       </c>
       <c r="D113" s="2">
-        <v>13100</v>
+        <f t="shared" si="2"/>
+        <v>8400</v>
       </c>
       <c r="E113" s="2">
-        <v>238</v>
+        <f t="shared" si="3"/>
+        <v>44</v>
       </c>
       <c r="F113" s="2">
         <v>2</v>
@@ -10898,10 +11118,12 @@
         <v>392</v>
       </c>
       <c r="D114" s="2">
-        <v>13100</v>
+        <f t="shared" si="2"/>
+        <v>8400</v>
       </c>
       <c r="E114" s="2">
-        <v>238</v>
+        <f t="shared" si="3"/>
+        <v>44</v>
       </c>
       <c r="F114" s="2">
         <v>2</v>
@@ -10954,10 +11176,12 @@
         <v>394</v>
       </c>
       <c r="D115" s="2">
-        <v>13100</v>
+        <f t="shared" si="2"/>
+        <v>8400</v>
       </c>
       <c r="E115" s="2">
-        <v>238</v>
+        <f t="shared" si="3"/>
+        <v>44</v>
       </c>
       <c r="F115" s="2">
         <v>2</v>
@@ -11010,10 +11234,12 @@
         <v>396</v>
       </c>
       <c r="D116" s="2">
-        <v>13100</v>
+        <f t="shared" si="2"/>
+        <v>8400</v>
       </c>
       <c r="E116" s="2">
-        <v>238</v>
+        <f t="shared" si="3"/>
+        <v>44</v>
       </c>
       <c r="F116" s="2">
         <v>2</v>
@@ -11066,10 +11292,12 @@
         <v>398</v>
       </c>
       <c r="D117" s="2">
-        <v>13100</v>
+        <f t="shared" si="2"/>
+        <v>8400</v>
       </c>
       <c r="E117" s="2">
-        <v>238</v>
+        <f t="shared" si="3"/>
+        <v>44</v>
       </c>
       <c r="F117" s="2">
         <v>2</v>
@@ -11122,10 +11350,12 @@
         <v>400</v>
       </c>
       <c r="D118" s="2">
-        <v>13100</v>
+        <f t="shared" si="2"/>
+        <v>8400</v>
       </c>
       <c r="E118" s="2">
-        <v>238</v>
+        <f t="shared" si="3"/>
+        <v>44</v>
       </c>
       <c r="F118" s="2">
         <v>2</v>
@@ -11178,10 +11408,12 @@
         <v>9</v>
       </c>
       <c r="D119" s="2">
-        <v>14000</v>
+        <f t="shared" si="2"/>
+        <v>8700</v>
       </c>
       <c r="E119" s="2">
-        <v>275</v>
+        <f t="shared" si="3"/>
+        <v>47</v>
       </c>
       <c r="F119" s="2">
         <v>1</v>
@@ -11234,10 +11466,12 @@
         <v>403</v>
       </c>
       <c r="D120" s="2">
-        <v>14000</v>
+        <f t="shared" si="2"/>
+        <v>8700</v>
       </c>
       <c r="E120" s="2">
-        <v>275</v>
+        <f t="shared" si="3"/>
+        <v>47</v>
       </c>
       <c r="F120" s="2">
         <v>1</v>
@@ -11290,10 +11524,12 @@
         <v>405</v>
       </c>
       <c r="D121" s="2">
-        <v>14000</v>
+        <f t="shared" si="2"/>
+        <v>8700</v>
       </c>
       <c r="E121" s="2">
-        <v>275</v>
+        <f t="shared" si="3"/>
+        <v>47</v>
       </c>
       <c r="F121" s="2">
         <v>1</v>
@@ -11346,10 +11582,12 @@
         <v>407</v>
       </c>
       <c r="D122" s="2">
-        <v>14000</v>
+        <f t="shared" si="2"/>
+        <v>8700</v>
       </c>
       <c r="E122" s="2">
-        <v>275</v>
+        <f t="shared" si="3"/>
+        <v>47</v>
       </c>
       <c r="F122" s="2">
         <v>1</v>
@@ -11402,10 +11640,12 @@
         <v>409</v>
       </c>
       <c r="D123" s="2">
-        <v>14000</v>
+        <f t="shared" si="2"/>
+        <v>8700</v>
       </c>
       <c r="E123" s="2">
-        <v>275</v>
+        <f t="shared" si="3"/>
+        <v>47</v>
       </c>
       <c r="F123" s="2">
         <v>1</v>
@@ -11458,10 +11698,12 @@
         <v>74</v>
       </c>
       <c r="D124" s="2">
-        <v>14000</v>
+        <f t="shared" si="2"/>
+        <v>8700</v>
       </c>
       <c r="E124" s="2">
-        <v>275</v>
+        <f t="shared" si="3"/>
+        <v>47</v>
       </c>
       <c r="F124" s="2">
         <v>1</v>
@@ -11514,10 +11756,12 @@
         <v>412</v>
       </c>
       <c r="D125" s="2">
-        <v>14000</v>
+        <f t="shared" si="2"/>
+        <v>8700</v>
       </c>
       <c r="E125" s="2">
-        <v>275</v>
+        <f t="shared" si="3"/>
+        <v>47</v>
       </c>
       <c r="F125" s="2">
         <v>1</v>
@@ -11570,10 +11814,12 @@
         <v>414</v>
       </c>
       <c r="D126" s="2">
-        <v>14000</v>
+        <f t="shared" si="2"/>
+        <v>8700</v>
       </c>
       <c r="E126" s="2">
-        <v>275</v>
+        <f t="shared" si="3"/>
+        <v>47</v>
       </c>
       <c r="F126" s="2">
         <v>1</v>
@@ -11626,10 +11872,12 @@
         <v>416</v>
       </c>
       <c r="D127" s="2">
-        <v>14000</v>
+        <f t="shared" si="2"/>
+        <v>8700</v>
       </c>
       <c r="E127" s="2">
-        <v>275</v>
+        <f t="shared" si="3"/>
+        <v>47</v>
       </c>
       <c r="F127" s="2">
         <v>1</v>
@@ -11682,10 +11930,12 @@
         <v>418</v>
       </c>
       <c r="D128" s="2">
-        <v>14000</v>
+        <f t="shared" si="2"/>
+        <v>8700</v>
       </c>
       <c r="E128" s="2">
-        <v>275</v>
+        <f t="shared" si="3"/>
+        <v>47</v>
       </c>
       <c r="F128" s="2">
         <v>1</v>
@@ -11738,10 +11988,12 @@
         <v>420</v>
       </c>
       <c r="D129" s="2">
-        <v>15000</v>
+        <f t="shared" si="2"/>
+        <v>9000</v>
       </c>
       <c r="E129" s="2">
-        <v>320</v>
+        <f t="shared" si="3"/>
+        <v>50</v>
       </c>
       <c r="F129" s="2">
         <v>0</v>
@@ -11794,10 +12046,12 @@
         <v>422</v>
       </c>
       <c r="D130" s="2">
-        <v>15000</v>
+        <f t="shared" si="2"/>
+        <v>9000</v>
       </c>
       <c r="E130" s="2">
-        <v>320</v>
+        <f t="shared" si="3"/>
+        <v>50</v>
       </c>
       <c r="F130" s="2">
         <v>0</v>
@@ -11850,10 +12104,12 @@
         <v>424</v>
       </c>
       <c r="D131" s="2">
-        <v>15000</v>
+        <f t="shared" si="2"/>
+        <v>9000</v>
       </c>
       <c r="E131" s="2">
-        <v>320</v>
+        <f t="shared" si="3"/>
+        <v>50</v>
       </c>
       <c r="F131" s="2">
         <v>0</v>
@@ -11906,10 +12162,12 @@
         <v>426</v>
       </c>
       <c r="D132" s="2">
-        <v>15000</v>
+        <f t="shared" si="2"/>
+        <v>9000</v>
       </c>
       <c r="E132" s="2">
-        <v>320</v>
+        <f t="shared" si="3"/>
+        <v>50</v>
       </c>
       <c r="F132" s="2">
         <v>0</v>
@@ -11962,10 +12220,12 @@
         <v>428</v>
       </c>
       <c r="D133" s="2">
-        <v>15000</v>
+        <f t="shared" si="2"/>
+        <v>9000</v>
       </c>
       <c r="E133" s="2">
-        <v>320</v>
+        <f t="shared" si="3"/>
+        <v>50</v>
       </c>
       <c r="F133" s="2">
         <v>0</v>
@@ -12018,10 +12278,12 @@
         <v>430</v>
       </c>
       <c r="D134" s="2">
-        <v>15000</v>
+        <f t="shared" si="2"/>
+        <v>9000</v>
       </c>
       <c r="E134" s="2">
-        <v>320</v>
+        <f t="shared" si="3"/>
+        <v>50</v>
       </c>
       <c r="F134" s="2">
         <v>0</v>
@@ -12074,10 +12336,12 @@
         <v>432</v>
       </c>
       <c r="D135" s="2">
-        <v>15000</v>
+        <f t="shared" ref="D135" si="4">$D$5+(15-F135)*300</f>
+        <v>9000</v>
       </c>
       <c r="E135" s="2">
-        <v>320</v>
+        <f t="shared" ref="E135" si="5">$E$5+(15-F135)*3</f>
+        <v>50</v>
       </c>
       <c r="F135" s="2">
         <v>0</v>
